--- a/266/food/tm2026-sm.xlsx
+++ b/266/food/tm2026-sm.xlsx
@@ -3,33 +3,24 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <charset val="204"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -125,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -400,14 +391,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -418,6 +420,30 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -454,68 +480,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -524,169 +502,159 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1078,7 +1046,8 @@
     <col width="6.85546875" customWidth="1" style="2" min="9" max="9"/>
     <col width="8.140625" customWidth="1" style="2" min="10" max="10"/>
     <col width="10" customWidth="1" style="2" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="2" min="12" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="12" max="12"/>
+    <col width="9.140625" customWidth="1" style="2" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1087,13 +1056,13 @@
           <t>Школа</t>
         </is>
       </c>
-      <c r="C1" s="52" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>МБОУ «СОШ №2 г.Шали»</t>
         </is>
       </c>
-      <c r="D1" s="58" t="n"/>
-      <c r="E1" s="59" t="n"/>
+      <c r="D1" s="55" t="n"/>
+      <c r="E1" s="56" t="n"/>
       <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Утвердил:</t>
@@ -1104,14 +1073,14 @@
           <t>должность</t>
         </is>
       </c>
-      <c r="H1" s="54" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>Директор</t>
         </is>
       </c>
-      <c r="I1" s="58" t="n"/>
-      <c r="J1" s="58" t="n"/>
-      <c r="K1" s="59" t="n"/>
+      <c r="I1" s="55" t="n"/>
+      <c r="J1" s="55" t="n"/>
+      <c r="K1" s="56" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
@@ -1125,14 +1094,14 @@
           <t>фамилия</t>
         </is>
       </c>
-      <c r="H2" s="54" t="inlineStr">
+      <c r="H2" s="57" t="inlineStr">
         <is>
           <t>Салаватова Амина Дадашевна</t>
         </is>
       </c>
-      <c r="I2" s="58" t="n"/>
-      <c r="J2" s="58" t="n"/>
-      <c r="K2" s="59" t="n"/>
+      <c r="I2" s="55" t="n"/>
+      <c r="J2" s="55" t="n"/>
+      <c r="K2" s="56" t="n"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1705,12 +1674,12 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D24" s="61" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="31" t="n"/>
       <c r="F24" s="32">
         <f>F13+F23</f>
@@ -2177,12 +2146,12 @@
         <f>B25</f>
         <v/>
       </c>
-      <c r="C43" s="60" t="inlineStr">
+      <c r="C43" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D43" s="61" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="31" t="n"/>
       <c r="F43" s="32">
         <f>F32+F42</f>
@@ -2671,12 +2640,12 @@
         <f>B44</f>
         <v/>
       </c>
-      <c r="C62" s="60" t="inlineStr">
+      <c r="C62" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D62" s="61" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="31" t="n"/>
       <c r="F62" s="32">
         <f>F51+F61</f>
@@ -3165,12 +3134,12 @@
         <f>B63</f>
         <v/>
       </c>
-      <c r="C81" s="60" t="inlineStr">
+      <c r="C81" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D81" s="61" t="n"/>
+      <c r="D81" s="53" t="n"/>
       <c r="E81" s="31" t="n"/>
       <c r="F81" s="32">
         <f>F70+F80</f>
@@ -3663,12 +3632,12 @@
         <f>B82</f>
         <v/>
       </c>
-      <c r="C100" s="60" t="inlineStr">
+      <c r="C100" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D100" s="61" t="n"/>
+      <c r="D100" s="53" t="n"/>
       <c r="E100" s="31" t="n"/>
       <c r="F100" s="32">
         <f>F89+F99</f>
@@ -4183,12 +4152,12 @@
         <f>B101</f>
         <v/>
       </c>
-      <c r="C119" s="60" t="inlineStr">
+      <c r="C119" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D119" s="61" t="n"/>
+      <c r="D119" s="53" t="n"/>
       <c r="E119" s="31" t="n"/>
       <c r="F119" s="32">
         <f>F108+F118</f>
@@ -4655,12 +4624,12 @@
         <f>B120</f>
         <v/>
       </c>
-      <c r="C138" s="60" t="inlineStr">
+      <c r="C138" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D138" s="61" t="n"/>
+      <c r="D138" s="53" t="n"/>
       <c r="E138" s="31" t="n"/>
       <c r="F138" s="32">
         <f>F127+F137</f>
@@ -5149,12 +5118,12 @@
         <f>B139</f>
         <v/>
       </c>
-      <c r="C157" s="60" t="inlineStr">
+      <c r="C157" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D157" s="61" t="n"/>
+      <c r="D157" s="53" t="n"/>
       <c r="E157" s="31" t="n"/>
       <c r="F157" s="32">
         <f>F146+F156</f>
@@ -5645,12 +5614,12 @@
         <f>B158</f>
         <v/>
       </c>
-      <c r="C176" s="60" t="inlineStr">
+      <c r="C176" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D176" s="61" t="n"/>
+      <c r="D176" s="53" t="n"/>
       <c r="E176" s="31" t="n"/>
       <c r="F176" s="32">
         <f>F165+F175</f>
@@ -6139,12 +6108,12 @@
         <f>B177</f>
         <v/>
       </c>
-      <c r="C195" s="60" t="inlineStr">
+      <c r="C195" s="52" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D195" s="61" t="n"/>
+      <c r="D195" s="53" t="n"/>
       <c r="E195" s="31" t="n"/>
       <c r="F195" s="32">
         <f>F184+F194</f>
@@ -6175,13 +6144,13 @@
     <row r="196" ht="13.5" customHeight="1" thickBot="1">
       <c r="A196" s="27" t="n"/>
       <c r="B196" s="28" t="n"/>
-      <c r="C196" s="57" t="inlineStr">
+      <c r="C196" s="58" t="inlineStr">
         <is>
           <t>Среднее значение за период:</t>
         </is>
       </c>
-      <c r="D196" s="62" t="n"/>
-      <c r="E196" s="63" t="n"/>
+      <c r="D196" s="59" t="n"/>
+      <c r="E196" s="60" t="n"/>
       <c r="F196" s="34">
         <f>(F24+F43+F62+F81+F100+F119+F138+F157+F176+F195)/(IF(F24=0,0,1)+IF(F43=0,0,1)+IF(F62=0,0,1)+IF(F81=0,0,1)+IF(F100=0,0,1)+IF(F119=0,0,1)+IF(F138=0,0,1)+IF(F157=0,0,1)+IF(F176=0,0,1)+IF(F195=0,0,1))</f>
         <v/>
@@ -6214,9 +6183,9 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C138:D138"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="H2:K2"/>

--- a/266/food/tm2026-sm.xlsx
+++ b/266/food/tm2026-sm.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7935" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,11 +16,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <charset val="204"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -116,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -391,6 +400,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -409,6 +431,26 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -431,41 +473,6 @@
       <left/>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -477,23 +484,38 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -502,159 +524,169 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1046,8 +1078,7 @@
     <col width="6.85546875" customWidth="1" style="2" min="9" max="9"/>
     <col width="8.140625" customWidth="1" style="2" min="10" max="10"/>
     <col width="10" customWidth="1" style="2" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="2" min="12" max="12"/>
-    <col width="9.140625" customWidth="1" style="2" min="13" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1056,13 +1087,13 @@
           <t>Школа</t>
         </is>
       </c>
-      <c r="C1" s="54" t="inlineStr">
+      <c r="C1" s="55" t="inlineStr">
         <is>
           <t>МБОУ «СОШ №2 г.Шали»</t>
         </is>
       </c>
-      <c r="D1" s="55" t="n"/>
-      <c r="E1" s="56" t="n"/>
+      <c r="D1" s="58" t="n"/>
+      <c r="E1" s="59" t="n"/>
       <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Утвердил:</t>
@@ -1078,9 +1109,9 @@
           <t>Директор</t>
         </is>
       </c>
-      <c r="I1" s="55" t="n"/>
-      <c r="J1" s="55" t="n"/>
-      <c r="K1" s="56" t="n"/>
+      <c r="I1" s="58" t="n"/>
+      <c r="J1" s="58" t="n"/>
+      <c r="K1" s="59" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
@@ -1099,9 +1130,9 @@
           <t>Салаватова Амина Дадашевна</t>
         </is>
       </c>
-      <c r="I2" s="55" t="n"/>
-      <c r="J2" s="55" t="n"/>
-      <c r="K2" s="56" t="n"/>
+      <c r="I2" s="58" t="n"/>
+      <c r="J2" s="58" t="n"/>
+      <c r="K2" s="59" t="n"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1674,12 +1705,12 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C24" s="52" t="inlineStr">
+      <c r="C24" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D24" s="53" t="n"/>
+      <c r="D24" s="61" t="n"/>
       <c r="E24" s="31" t="n"/>
       <c r="F24" s="32">
         <f>F13+F23</f>
@@ -2146,12 +2177,12 @@
         <f>B25</f>
         <v/>
       </c>
-      <c r="C43" s="52" t="inlineStr">
+      <c r="C43" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D43" s="53" t="n"/>
+      <c r="D43" s="61" t="n"/>
       <c r="E43" s="31" t="n"/>
       <c r="F43" s="32">
         <f>F32+F42</f>
@@ -2640,12 +2671,12 @@
         <f>B44</f>
         <v/>
       </c>
-      <c r="C62" s="52" t="inlineStr">
+      <c r="C62" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D62" s="53" t="n"/>
+      <c r="D62" s="61" t="n"/>
       <c r="E62" s="31" t="n"/>
       <c r="F62" s="32">
         <f>F51+F61</f>
@@ -3134,12 +3165,12 @@
         <f>B63</f>
         <v/>
       </c>
-      <c r="C81" s="52" t="inlineStr">
+      <c r="C81" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D81" s="53" t="n"/>
+      <c r="D81" s="61" t="n"/>
       <c r="E81" s="31" t="n"/>
       <c r="F81" s="32">
         <f>F70+F80</f>
@@ -3632,12 +3663,12 @@
         <f>B82</f>
         <v/>
       </c>
-      <c r="C100" s="52" t="inlineStr">
+      <c r="C100" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D100" s="53" t="n"/>
+      <c r="D100" s="61" t="n"/>
       <c r="E100" s="31" t="n"/>
       <c r="F100" s="32">
         <f>F89+F99</f>
@@ -4152,12 +4183,12 @@
         <f>B101</f>
         <v/>
       </c>
-      <c r="C119" s="52" t="inlineStr">
+      <c r="C119" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D119" s="53" t="n"/>
+      <c r="D119" s="61" t="n"/>
       <c r="E119" s="31" t="n"/>
       <c r="F119" s="32">
         <f>F108+F118</f>
@@ -4624,12 +4655,12 @@
         <f>B120</f>
         <v/>
       </c>
-      <c r="C138" s="52" t="inlineStr">
+      <c r="C138" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D138" s="53" t="n"/>
+      <c r="D138" s="61" t="n"/>
       <c r="E138" s="31" t="n"/>
       <c r="F138" s="32">
         <f>F127+F137</f>
@@ -5118,12 +5149,12 @@
         <f>B139</f>
         <v/>
       </c>
-      <c r="C157" s="52" t="inlineStr">
+      <c r="C157" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D157" s="53" t="n"/>
+      <c r="D157" s="61" t="n"/>
       <c r="E157" s="31" t="n"/>
       <c r="F157" s="32">
         <f>F146+F156</f>
@@ -5614,12 +5645,12 @@
         <f>B158</f>
         <v/>
       </c>
-      <c r="C176" s="52" t="inlineStr">
+      <c r="C176" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D176" s="53" t="n"/>
+      <c r="D176" s="61" t="n"/>
       <c r="E176" s="31" t="n"/>
       <c r="F176" s="32">
         <f>F165+F175</f>
@@ -6108,12 +6139,12 @@
         <f>B177</f>
         <v/>
       </c>
-      <c r="C195" s="52" t="inlineStr">
+      <c r="C195" s="60" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D195" s="53" t="n"/>
+      <c r="D195" s="61" t="n"/>
       <c r="E195" s="31" t="n"/>
       <c r="F195" s="32">
         <f>F184+F194</f>
@@ -6144,13 +6175,13 @@
     <row r="196" ht="13.5" customHeight="1" thickBot="1">
       <c r="A196" s="27" t="n"/>
       <c r="B196" s="28" t="n"/>
-      <c r="C196" s="58" t="inlineStr">
+      <c r="C196" s="54" t="inlineStr">
         <is>
           <t>Среднее значение за период:</t>
         </is>
       </c>
-      <c r="D196" s="59" t="n"/>
-      <c r="E196" s="60" t="n"/>
+      <c r="D196" s="62" t="n"/>
+      <c r="E196" s="63" t="n"/>
       <c r="F196" s="34">
         <f>(F24+F43+F62+F81+F100+F119+F138+F157+F176+F195)/(IF(F24=0,0,1)+IF(F43=0,0,1)+IF(F62=0,0,1)+IF(F81=0,0,1)+IF(F100=0,0,1)+IF(F119=0,0,1)+IF(F138=0,0,1)+IF(F157=0,0,1)+IF(F176=0,0,1)+IF(F195=0,0,1))</f>
         <v/>
@@ -6182,10 +6213,10 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C138:D138"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="H2:K2"/>
